--- a/naver-place-crawler/results_health/동래구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/동래구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>inthegym05@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1458-3783</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/inthegym05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1595</v>
+        <v>1077</v>
       </c>
       <c r="Q2" t="n">
-        <v>1739</v>
+        <v>334</v>
       </c>
       <c r="R2" t="n">
-        <v>3334</v>
+        <v>1411</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,56 +636,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1533075467</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1533075467</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
+          <t>피트니스인앤스타 헬스 &amp; PT 피티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rlarjsdn12433@naver.com</t>
+          <t>fitnessinanstar_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1323-5243</t>
+          <t>0507-1372-0032</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천천로 391 1층 건담짐</t>
+          <t>부산광역시 동래구 온천장로 75 5층 피트니스 인앤스타</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlarjsdn12433</t>
+          <t>https://pf.kakao.com/_yxmwmb</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2858</v>
+        <v>532</v>
       </c>
       <c r="Q3" t="n">
-        <v>896</v>
+        <v>1552</v>
       </c>
       <c r="R3" t="n">
-        <v>3754</v>
+        <v>2084</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,24 +730,24 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1130935293</t>
+          <t>1010601856</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130935293</t>
+          <t>https://m.place.naver.com/place/1010601856</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q4" t="n">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="R4" t="n">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,41 +834,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
+          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inthegym05@naver.com</t>
+          <t>rlarjsdn12433@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1458-3783</t>
+          <t>0507-1323-5243</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
+          <t>부산광역시 동래구 온천천로 391 1층 건담짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inthegym05</t>
+          <t>https://blog.naver.com/rlarjsdn12433</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1061</v>
+        <v>2891</v>
       </c>
       <c r="Q5" t="n">
-        <v>322</v>
+        <v>901</v>
       </c>
       <c r="R5" t="n">
-        <v>1383</v>
+        <v>3792</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1533075467</t>
+          <t>1130935293</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533075467</t>
+          <t>https://m.place.naver.com/place/1130935293</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>잇짐 헬스&amp;PT 미남역점</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rkdgnltjd159@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1483-9683</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 우장춘로 7 보민빌딩 13층 잇짐</t>
+          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkdgnltjd159?tab=1</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>292</v>
+        <v>1613</v>
       </c>
       <c r="Q6" t="n">
-        <v>631</v>
+        <v>1750</v>
       </c>
       <c r="R6" t="n">
-        <v>923</v>
+        <v>3363</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1012,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1285911769</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285911769</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스인앤스타 헬스 &amp; PT 피티</t>
+          <t>APX 하이록스 공식 체육관</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fitnessinanstar_@naver.com</t>
+          <t>apx_hyrox@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1372-0032</t>
+          <t>0507-1402-1939</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천장로 75 5층 피트니스 인앤스타</t>
+          <t>부산광역시 동래구 사직로 54 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_yxmwmb</t>
+          <t>https://blog.naver.com/apx_hyrox</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>527</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1541</v>
+        <v>13</v>
       </c>
       <c r="R7" t="n">
-        <v>2068</v>
+        <v>20</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1106,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1010601856</t>
+          <t>2017547419</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010601856</t>
+          <t>https://m.place.naver.com/place/2017547419</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>옐로우필드 헬스,그룹PT</t>
+          <t>엠씨피트니스&amp;필라테스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yellow0934@naver.com</t>
+          <t>mcfitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1312-0939</t>
+          <t>0507-1388-0887</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로 225 4층</t>
+          <t>부산광역시 동래구 명륜로 161 네오앤바하 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yellow0934</t>
+          <t>http://pf.kakao.com/_Mxepzb/chat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>1593</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>928</v>
       </c>
       <c r="R8" t="n">
-        <v>64</v>
+        <v>2521</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1200,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2035900236</t>
+          <t>1934360629</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035900236</t>
+          <t>https://m.place.naver.com/place/1934360629</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>매드맥스 사직 PT&amp;그룹운동</t>
+          <t>바디디자인 헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dlckdwns501@naver.com</t>
+          <t>fammirl4@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1360-2526</t>
+          <t>051-528-0101</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 사직북로 5 지하1층</t>
+          <t>부산광역시 동래구 충렬대로428번길 62 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mad_sajik</t>
+          <t>https://www.instagram.com/bodydesign0101</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="Q9" t="n">
-        <v>507</v>
+        <v>76</v>
       </c>
       <c r="R9" t="n">
-        <v>686</v>
+        <v>133</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,66 +1294,66 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1376661165</t>
+          <t>1211329582</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1376661165</t>
+          <t>https://m.place.naver.com/place/1211329582</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모움피티 동래명륜점</t>
+          <t>그룹PT피트니스 리핏타운짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fright_4503@naver.com</t>
+          <t>refittowngymceo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1350-3063</t>
+          <t>0507-1438-1742</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천천로 71-1 3층</t>
+          <t>부산광역시 동래구 중앙대로1367번길 70-5 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://moumfitness.netlify.app/</t>
+          <t>https://blog.naver.com/refittowngymceo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>888</v>
+        <v>47</v>
       </c>
       <c r="R10" t="n">
-        <v>1019</v>
+        <v>77</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,56 +1388,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1380822781</t>
+          <t>2097433512</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1380822781</t>
+          <t>https://m.place.naver.com/place/2097433512</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>핏핏바디트레이닝 PT센터 동래점</t>
+          <t>유메짐PT 동래점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitfitness@naver.com</t>
+          <t>yumegym_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1336-5562</t>
+          <t>0507-1435-7181</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로 151 천일스카이원 2F</t>
+          <t>부산광역시 동래구 충렬대로 447 보성빌딩 5층 유메짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitfitness</t>
+          <t>https://yumegym-mo.imweb.me</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="n">
-        <v>833</v>
+        <v>414</v>
       </c>
       <c r="R11" t="n">
-        <v>1209</v>
+        <v>491</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,957 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1987666419</t>
+          <t>1294548420</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987666419</t>
+          <t>https://m.place.naver.com/place/1294548420</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>피티시즌</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ptmap@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1315-7707</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 사직북로 3 4층 피티 시즌</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ptmap</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>109</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>258</v>
-      </c>
-      <c r="R12" t="n">
-        <v>367</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1264708260</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1264708260</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>잇츠짐플러스</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>kys5567@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1397-1311</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 중앙대로 1523 홈플러스동래점 지하2층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>304</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>304</v>
-      </c>
-      <c r="R13" t="n">
-        <v>608</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>38323087</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/38323087</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>첼시피트니스&amp;PT 사직점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>wannagym_sajik@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1446-9106</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 쇠미로60번길 53 지하1층 첼시 피트니스 사직점</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/chelseafitness_sajik_/</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>77</v>
-      </c>
-      <c r="R14" t="n">
-        <v>159</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2083713807</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2083713807</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>이진호수휘트니스</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>su_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>051-503-2425</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 충렬대로 110 2층 이진호수휘트니스</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/su_fitness</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>124</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>641</v>
-      </c>
-      <c r="R15" t="n">
-        <v>765</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1528156267</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1528156267</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>엠씨피트니스&amp;필라테스&amp;PT 동래점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>mcfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1388-0887</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 명륜로 161 네오앤바하 2층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_Mxepzb/chat</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1576</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>921</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2497</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1934360629</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1934360629</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>이도피트니스 안락점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2do_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1362-3361</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 충렬대로 420 안락종합타운 2층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/2do_fitness_4</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>217</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>72</v>
-      </c>
-      <c r="R17" t="n">
-        <v>289</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2030253276</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2030253276</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>APX 하이록스 공식 체육관</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>apx_hyrox@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1402-1939</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 사직로 54 4층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/apx_hyrox</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>19</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2017547419</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2017547419</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>스카이짐24H &amp; 기구필라테스</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>km3993@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1483-5661</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 안남로 108 화성코아 2층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>http://www.skygym.co.kr</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>2708</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>338</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3046</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>38521265</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/38521265</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>크로스핏 에이치</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>cokehan90@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1355-0739</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 충렬대로 110 지하1층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/coke_han</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>50</v>
-      </c>
-      <c r="R20" t="n">
-        <v>83</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1194038287</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1194038287</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>커스텀피트니스 사직점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>customfitness3@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1411-0779</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>부산광역시 동래구 사직북로 4 지하 1층 커스텀피트니스 사직점</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/customfitness_sajik/</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>584</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>261</v>
-      </c>
-      <c r="R21" t="n">
-        <v>845</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1290468945</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1290468945</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/동래구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/동래구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="Q2" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="R2" t="n">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스인앤스타 헬스 &amp; PT 피티</t>
+          <t>윤피티앤짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitnessinanstar_@naver.com</t>
+          <t>yunpt-gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1372-0032</t>
+          <t>0507-1391-9943</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천장로 75 5층 피트니스 인앤스타</t>
+          <t>부산 금정구 부산대학로49번길 33-3 1층 좌측</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_yxmwmb</t>
+          <t>https://blog.naver.com/yunpt-gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,33 +695,37 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpgkdoj</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>532</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="n">
-        <v>1552</v>
+        <v>43</v>
       </c>
       <c r="R3" t="n">
-        <v>2084</v>
+        <v>93</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1010601856</t>
+          <t>1010289296</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010601856</t>
+          <t>https://m.place.naver.com/place/1010289296</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -812,10 +816,10 @@
         <v>168</v>
       </c>
       <c r="Q4" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="R4" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,34 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
+          <t>피트니스인앤스타 헬스 &amp; PT 피티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rlarjsdn12433@naver.com</t>
+          <t>fitnessinanstar_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1323-5243</t>
+          <t>0507-1372-0032</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천천로 391 1층 건담짐</t>
+          <t>부산광역시 동래구 온천장로 75 5층 피트니스 인앤스타</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlarjsdn12433</t>
+          <t>https://pf.kakao.com/_yxmwmb</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2891</v>
+        <v>532</v>
       </c>
       <c r="Q5" t="n">
-        <v>901</v>
+        <v>1553</v>
       </c>
       <c r="R5" t="n">
-        <v>3792</v>
+        <v>2085</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +922,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1130935293</t>
+          <t>1010601856</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130935293</t>
+          <t>https://m.place.naver.com/place/1010601856</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>rlarjsdn12433@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1323-5243</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산광역시 동래구 온천천로 391 1층 건담짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/rlarjsdn12433</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1613</v>
+        <v>2894</v>
       </c>
       <c r="Q6" t="n">
-        <v>1750</v>
+        <v>901</v>
       </c>
       <c r="R6" t="n">
-        <v>3363</v>
+        <v>3795</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1016,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1130935293</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1130935293</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APX 하이록스 공식 체육관</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>apx_hyrox@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1402-1939</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 사직로 54 4층</t>
+          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/apx_hyrox</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>1615</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>1753</v>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>3368</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2017547419</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2017547419</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엠씨피트니스&amp;필라테스&amp;PT 동래점</t>
+          <t>APX 하이록스 공식 체육관</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mcfitness@naver.com</t>
+          <t>apx_hyrox@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1388-0887</t>
+          <t>0507-1402-1939</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로 161 네오앤바하 2층</t>
+          <t>부산광역시 동래구 사직로 54 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Mxepzb/chat</t>
+          <t>https://blog.naver.com/apx_hyrox</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1593</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>928</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>2521</v>
+        <v>20</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1934360629</t>
+          <t>2017547419</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934360629</t>
+          <t>https://m.place.naver.com/place/2017547419</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디디자인 헬스PT</t>
+          <t>커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fammirl4@naver.com</t>
+          <t>customfitness3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>051-528-0101</t>
+          <t>0507-1411-0779</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 충렬대로428번길 62 4층</t>
+          <t>부산광역시 동래구 사직북로 4 지하 1층 커스텀피트니스 사직점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodydesign0101</t>
+          <t>https://www.instagram.com/customfitness_sajik/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>57</v>
+        <v>594</v>
       </c>
       <c r="Q9" t="n">
-        <v>76</v>
+        <v>264</v>
       </c>
       <c r="R9" t="n">
-        <v>133</v>
+        <v>858</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1211329582</t>
+          <t>1290468945</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1211329582</t>
+          <t>https://m.place.naver.com/place/1290468945</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>그룹PT피트니스 리핏타운짐</t>
+          <t>바디디자인 헬스PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>refittowngymceo@naver.com</t>
+          <t>fammirl4@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1438-1742</t>
+          <t>051-528-0101</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 중앙대로1367번길 70-5 B1층</t>
+          <t>부산광역시 동래구 충렬대로428번길 62 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refittowngymceo</t>
+          <t>https://www.instagram.com/bodydesign0101</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="Q10" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="R10" t="n">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2097433512</t>
+          <t>1211329582</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097433512</t>
+          <t>https://m.place.naver.com/place/1211329582</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1470,10 +1474,10 @@
         <v>77</v>
       </c>
       <c r="Q11" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R11" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1492,7 +1496,101 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>더온피트니스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>theonfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1425-0269</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산광역시 동래구 우장춘로 14 10층 더온피트니스</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theon_fitnes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>444</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1410321571</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1410321571</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
